--- a/output/pdf_financials_xlsx/IPCO.xlsx
+++ b/output/pdf_financials_xlsx/IPCO.xlsx
@@ -1591,34 +1591,34 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>0</v>
+        <v>0.11751</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0</v>
+        <v>0.087162</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0</v>
+        <v>0.1257</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0</v>
+        <v>0.146255</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0</v>
+        <v>0.12528</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0</v>
+        <v>0.130837</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0</v>
+        <v>0.134436</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0</v>
+        <v>0.111303</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0</v>
+        <v>0.138566</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0</v>
+        <v>0.129754</v>
       </c>
     </row>
     <row r="29">
@@ -4341,34 +4341,34 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>0.11751</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>0.087162</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.1257</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>0.146255</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>0.12528</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>0.130837</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>0.134436</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>0.111303</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>0.138566</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>0.129754</v>
       </c>
     </row>
     <row r="101">
@@ -5253,10 +5253,10 @@
         <v>0</v>
       </c>
       <c r="J124" s="3" t="n">
-        <v>0</v>
+        <v>-0.000964</v>
       </c>
       <c r="K124" s="3" t="n">
-        <v>0</v>
+        <v>-0.000976</v>
       </c>
     </row>
     <row r="125">
@@ -5290,10 +5290,10 @@
         <v>0</v>
       </c>
       <c r="J125" s="3" t="n">
-        <v>0</v>
+        <v>-0.000964</v>
       </c>
       <c r="K125" s="3" t="n">
-        <v>0</v>
+        <v>-0.000976</v>
       </c>
     </row>
     <row r="126">
@@ -12564,7 +12564,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -14378,7 +14378,11 @@
           <t>Lease payment</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr"/>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E139" t="inlineStr">
         <is>
           <t>-</t>
@@ -14996,7 +15000,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -16672,7 +16676,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -17638,7 +17642,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E191" s="5" t="n">
@@ -22456,7 +22460,7 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
@@ -27164,7 +27168,7 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E342" s="5" t="n">

--- a/output/pdf_financials_xlsx/IPCO.xlsx
+++ b/output/pdf_financials_xlsx/IPCO.xlsx
@@ -1036,7 +1036,7 @@
         <v>0.019248</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.03382</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>0.021684</v>
@@ -3104,34 +3104,34 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.003682</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.007056</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.035142</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.040317</v>
       </c>
       <c r="F67" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.045329</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.078206</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.118912</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.119316</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.09440999999999999</v>
       </c>
     </row>
     <row r="68">
@@ -3141,34 +3141,34 @@
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>0.022924</v>
+        <v>0.026606</v>
       </c>
       <c r="C68" s="3" t="n">
-        <v>0.057388</v>
+        <v>0.064444</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>0.077615</v>
+        <v>0.112757</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>0.085826</v>
+        <v>0.126143</v>
       </c>
       <c r="F68" s="3" t="n">
         <v>0.06335</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0.079841</v>
+        <v>0.12517</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>0.118726</v>
+        <v>0.196932</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>0.188871</v>
+        <v>0.307783</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0.176371</v>
+        <v>0.295687</v>
       </c>
       <c r="K68" s="3" t="n">
-        <v>0.149708</v>
+        <v>0.244118</v>
       </c>
     </row>
     <row r="69">
@@ -3224,25 +3224,25 @@
         <v>0</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>0</v>
+        <v>0.000844</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>0</v>
+        <v>0.000671</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>0</v>
+        <v>0.000684</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>0</v>
+        <v>0.000752</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>0</v>
+        <v>0.000809</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>0</v>
+        <v>0.0005730000000000001</v>
       </c>
       <c r="K70" s="3" t="n">
-        <v>0</v>
+        <v>0.0009300000000000001</v>
       </c>
     </row>
     <row r="71">
@@ -3261,25 +3261,25 @@
         <v>0</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>0</v>
+        <v>0.000844</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>0</v>
+        <v>0.000671</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0</v>
+        <v>0.000684</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>0</v>
+        <v>0.000752</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>0</v>
+        <v>0.000809</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>0</v>
+        <v>0.0005730000000000001</v>
       </c>
       <c r="K71" s="3" t="n">
-        <v>0</v>
+        <v>0.0009300000000000001</v>
       </c>
     </row>
     <row r="72">
@@ -3400,34 +3400,34 @@
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>0.003815</v>
+        <v>0.000133</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>0.006284</v>
+        <v>0</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>0.0187</v>
+        <v>0</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>0.013806</v>
+        <v>0</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>0.033787</v>
+        <v>0.033116</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.015138</v>
+        <v>0</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>0.031179</v>
+        <v>0</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>0.014017</v>
+        <v>0</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>0.031707</v>
+        <v>0</v>
       </c>
       <c r="K75" s="3" t="n">
-        <v>0.01054</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -3600,25 +3600,25 @@
         </is>
       </c>
       <c r="E80" s="3" t="n">
-        <v>0.001396704334693154</v>
+        <v>0.002015182014903554</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>0.001010411665866539</v>
+        <v>0.0015137421987518</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>0.0007694276557423642</v>
+        <v>0.001306456754240096</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>0.0003018545299315261</v>
+        <v>0.0007495756473053083</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>0.001011640898988602</v>
+        <v>0.001403791108515089</v>
       </c>
       <c r="J80" s="3" t="n">
-        <v>0.001396337786804608</v>
+        <v>0.001689630144516866</v>
       </c>
       <c r="K80" s="3" t="n">
-        <v>0.00149471918140359</v>
+        <v>0.00196497927568821</v>
       </c>
     </row>
     <row r="81">
@@ -5121,7 +5121,7 @@
         <v>0</v>
       </c>
       <c r="C121" s="3" t="n">
-        <v>0</v>
+        <v>-0.090632</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>0</v>
@@ -7386,7 +7386,11 @@
           <t>Lease liabilities 10</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>-</t>
@@ -9064,7 +9068,11 @@
           <t>Lease liabilities 11</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
           <t>-</t>
@@ -10742,7 +10750,11 @@
           <t>Lease liabilities 12</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
           <t>-</t>
@@ -20982,7 +20994,11 @@
           <t>Share purchase</t>
         </is>
       </c>
-      <c r="D243" t="inlineStr"/>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E243" t="inlineStr">
         <is>
           <t>-</t>
@@ -23924,7 +23940,11 @@
           <t>Income tax recovery / (expense) 7</t>
         </is>
       </c>
-      <c r="D292" t="inlineStr"/>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E292" t="inlineStr">
         <is>
           <t>-</t>
